--- a/01_Raw_Data/Existing_Advisories_2026.xlsx
+++ b/01_Raw_Data/Existing_Advisories_2026.xlsx
@@ -16,14 +16,14 @@
     <sheet name="2024_Statewide_Hg" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Site Specific Advisories 26'!$A$1:$E$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Site Specific Advisories 26'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="98">
   <si>
     <t>2 servings/month</t>
   </si>
@@ -277,9 +277,6 @@
     <t>Freshwater Drum</t>
   </si>
   <si>
-    <t>any</t>
-  </si>
-  <si>
     <t>Unrestricted</t>
   </si>
   <si>
@@ -307,27 +304,6 @@
     <t>Chatfield Reservoir</t>
   </si>
   <si>
-    <t>bigger than 10 inches</t>
-  </si>
-  <si>
-    <t>bigger than 11 inches</t>
-  </si>
-  <si>
-    <t>bigger than 18 inches</t>
-  </si>
-  <si>
-    <t>bigger than 12 inches</t>
-  </si>
-  <si>
-    <t>bigger than 13 inches</t>
-  </si>
-  <si>
-    <t>bigger than 8 inches</t>
-  </si>
-  <si>
-    <t>bigger than 15 inches</t>
-  </si>
-  <si>
     <t>Runyon Lake</t>
   </si>
   <si>
@@ -338,6 +314,9 @@
   </si>
   <si>
     <t>Shadow Mountain Reservoir</t>
+  </si>
+  <si>
+    <t>Big</t>
   </si>
 </sst>
 </file>
@@ -378,6 +357,7 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Trebuchet MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -897,36 +877,42 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="13" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -934,1447 +920,1401 @@
         <v>57</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C4" s="13"/>
       <c r="D4" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C5" s="13"/>
       <c r="D5" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C6" s="13"/>
       <c r="D6" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C7" s="13"/>
       <c r="D7" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C8" s="13"/>
       <c r="D8" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="13" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C9" s="13"/>
       <c r="D9" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="13" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C10" s="13"/>
       <c r="D10" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="13" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C11" s="13"/>
       <c r="D11" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="13" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C12" s="13"/>
       <c r="D12" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>85</v>
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F13">
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="13" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F17">
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="13" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F18">
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="13" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C21" s="13"/>
       <c r="D21" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F21">
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="13" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C22" s="13"/>
       <c r="D22" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="13" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C23" s="13"/>
       <c r="D23" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C24" s="13"/>
       <c r="D24" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F24">
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C25" s="13"/>
       <c r="D25" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F25">
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="13" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C26" s="13"/>
       <c r="D26" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F26">
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="13" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C27" s="13"/>
       <c r="D27" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="F27">
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="13" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C28" s="13"/>
       <c r="D28" s="14" t="s">
         <v>1</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="13" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C29" s="13"/>
       <c r="D29" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="13" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C30" s="13"/>
       <c r="D30" s="14" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="13" t="s">
-        <v>102</v>
+        <v>37</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>100</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C31" s="13"/>
       <c r="D31" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="13" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>100</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C32" s="13"/>
       <c r="D32" s="14" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="13" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C33" s="13"/>
       <c r="D33" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="13" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C34" s="13"/>
       <c r="D34" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="13" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C35" s="13"/>
       <c r="D35" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="13" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C36" s="13"/>
       <c r="D36" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F36">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="13" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C37" s="13"/>
       <c r="D37" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="13" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C38" s="13"/>
       <c r="D38" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C39" s="13"/>
       <c r="D39" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F39">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C40" s="13"/>
       <c r="D40" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="13" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C41" s="13"/>
       <c r="D41" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="13" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C42" s="13"/>
       <c r="D42" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D43" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E43" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F43">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="13" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>2</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="13" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D47" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E47" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F47">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="13" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D48" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F48">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="13" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="13" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="13" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C52" s="13"/>
       <c r="D52" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E52" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F52">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="13" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C53" s="13"/>
       <c r="D53" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E53" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F53">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="13" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C54" s="13"/>
       <c r="D54" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="13" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C55" s="13"/>
       <c r="D55" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="13" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C56" s="13"/>
       <c r="D56" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E56" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F56">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="13" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>98</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C57" s="13"/>
       <c r="D57" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C58" s="13"/>
       <c r="D58" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E58" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E58" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F58">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="13" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C59" s="13"/>
       <c r="D59" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="13" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>97</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C60" s="13"/>
       <c r="D60" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="13" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>96</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C61" s="13"/>
       <c r="D61" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C62" s="13"/>
       <c r="D62" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E62" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F62">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="13" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C63" s="13"/>
       <c r="D63" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="13" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C64" s="13"/>
       <c r="D64" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E64" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F64">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C65" s="13"/>
       <c r="D65" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E65" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E65" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F65">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C66" s="13"/>
       <c r="D66" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E66" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F66">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C67" s="13"/>
       <c r="D67" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E67" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F67">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C68" s="13"/>
       <c r="D68" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C69" s="13"/>
       <c r="D69" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="13" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C70" s="13"/>
       <c r="D70" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="13" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>96</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C71" s="13"/>
       <c r="D71" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C72" s="13"/>
       <c r="D72" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C73" s="13"/>
       <c r="D73" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E73" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E73" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F73">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>94</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C74" s="13"/>
       <c r="D74" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C75" s="13"/>
       <c r="D75" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F75">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C76" s="13"/>
       <c r="D76" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E76" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F76">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C77" s="13"/>
       <c r="D77" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C78" s="13"/>
       <c r="D78" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>95</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C79" s="13"/>
       <c r="D79" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2382,59 +2322,53 @@
         <v>26</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C80" s="13"/>
       <c r="D80" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E80" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F80">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="13" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C81" s="13"/>
       <c r="D81" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E81" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F81">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="13" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C82" s="13" t="s">
-        <v>94</v>
-      </c>
+      <c r="C82" s="13"/>
       <c r="D82" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F82">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2444,37 +2378,33 @@
       <c r="B83" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C83" s="13" t="s">
-        <v>84</v>
-      </c>
+      <c r="C83" s="13"/>
       <c r="D83" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F83">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C84" s="13"/>
       <c r="D84" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F84">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2482,19 +2412,17 @@
         <v>21</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C85" s="13"/>
       <c r="D85" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E85" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F85">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2502,119 +2430,107 @@
         <v>21</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C86" s="13"/>
       <c r="D86" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E86" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E86" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F86">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C87" s="13"/>
       <c r="D87" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E87" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E87" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F87">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="13" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C88" s="13"/>
       <c r="D88" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E88" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E88" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F88">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C89" s="13"/>
       <c r="D89" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="F89">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C90" s="13"/>
       <c r="D90" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E90" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E90" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F90">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C91" s="13"/>
       <c r="D91" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E91" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F91">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2622,293 +2538,269 @@
         <v>9</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C92" s="13"/>
       <c r="D92" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E92" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E92" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="F92">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="13" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="13" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>2</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F95">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="13" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C96" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C96" s="13"/>
       <c r="D96" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F96">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="13" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C97" s="13"/>
       <c r="D97" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F97">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="13" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C98" s="13"/>
       <c r="D98" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F98">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="13" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C99" s="13"/>
       <c r="D99" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F99">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="13" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C100" s="13"/>
       <c r="D100" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F100">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="13" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C101" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C101" s="13"/>
       <c r="D101" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="13" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C102" s="13"/>
       <c r="D102" s="14" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F102">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="13" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C103" s="13"/>
       <c r="D103" s="14" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F103">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="13" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B104" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C104" s="13" t="s">
-        <v>84</v>
-      </c>
+      <c r="C104" s="13"/>
       <c r="D104" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F104">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="13" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C105" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C105" s="13"/>
       <c r="D105" s="14" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F105">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="13" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="13" t="s">
-        <v>97</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C106" s="13"/>
       <c r="D106" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>0</v>
@@ -2919,16 +2811,14 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="13" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C107" s="13"/>
       <c r="D107" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>0</v>
@@ -2939,16 +2829,14 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="13" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C108" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C108" s="13"/>
       <c r="D108" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" s="14" t="s">
         <v>0</v>
@@ -2959,16 +2847,14 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="13" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C109" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C109" s="13"/>
       <c r="D109" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E109" s="14" t="s">
         <v>0</v>
@@ -2979,16 +2865,14 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="13" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C110" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C110" s="13"/>
       <c r="D110" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>0</v>
@@ -2999,16 +2883,14 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="13" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C111" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C111" s="13"/>
       <c r="D111" s="14" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E111" s="14" t="s">
         <v>0</v>
@@ -3019,16 +2901,14 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="13" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C112" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C112" s="13"/>
       <c r="D112" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E112" s="14" t="s">
         <v>0</v>
@@ -3039,16 +2919,14 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="13" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C113" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C113" s="13"/>
       <c r="D113" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E113" s="14" t="s">
         <v>0</v>
@@ -3059,16 +2937,14 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="13" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C114" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C114" s="13"/>
       <c r="D114" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="14" t="s">
         <v>0</v>
@@ -3079,16 +2955,14 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="13" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C115" s="13" t="s">
-        <v>96</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C115" s="13"/>
       <c r="D115" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E115" s="14" t="s">
         <v>0</v>
@@ -3099,16 +2973,14 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="13" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C116" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C116" s="13"/>
       <c r="D116" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E116" s="14" t="s">
         <v>0</v>
@@ -3119,14 +2991,12 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="13" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C117" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C117" s="13"/>
       <c r="D117" s="14" t="s">
         <v>1</v>
       </c>
@@ -3139,16 +3009,14 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="13" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C118" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C118" s="13"/>
       <c r="D118" s="14" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E118" s="14" t="s">
         <v>0</v>
@@ -3159,16 +3027,14 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="13" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C119" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C119" s="13"/>
       <c r="D119" s="14" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="E119" s="14" t="s">
         <v>0</v>
@@ -3179,347 +3045,321 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="13" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C120" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C120" s="13"/>
       <c r="D120" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F120">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="13" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C121" s="13" t="s">
-        <v>96</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C121" s="13"/>
       <c r="D121" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F121">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="13" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C122" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C122" s="13"/>
       <c r="D122" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F122">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="13" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C123" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C123" s="13"/>
       <c r="D123" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F123">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="13" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C124" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C124" s="13"/>
       <c r="D124" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F124">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="13" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C125" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C125" s="13"/>
       <c r="D125" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="13" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C126" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C126" s="13"/>
       <c r="D126" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F126">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="13" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="B127" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C127" s="13" t="s">
-        <v>84</v>
-      </c>
+      <c r="C127" s="13"/>
       <c r="D127" s="14" t="s">
         <v>2</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F127">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="13" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C128" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C128" s="13"/>
       <c r="D128" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F128">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="13" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C129" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C129" s="13"/>
       <c r="D129" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E129" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F129">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="13" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C130" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C130" s="13"/>
       <c r="D130" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F130">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="13" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C131" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C131" s="13"/>
       <c r="D131" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F131">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="13" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C132" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C132" s="13"/>
       <c r="D132" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E132" s="14" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F132">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="13" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F133">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="13" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="13" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F135">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C136" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E136" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B137" s="13" t="s">
         <v>6</v>
@@ -3528,1739 +3368,1501 @@
         <v>97</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E137" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="13" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="13" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="13" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D140" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F140">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="13" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D141" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E141" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F141">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="13" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C142" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C142" s="13"/>
       <c r="D142" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F142">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="13" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C143" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C143" s="13"/>
       <c r="D143" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E143" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F143">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="13" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C144" s="13" t="s">
-        <v>100</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C144" s="13"/>
       <c r="D144" s="14" t="s">
         <v>2</v>
       </c>
       <c r="E144" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F144">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C145" s="13" t="s">
-        <v>99</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C145" s="13"/>
       <c r="D145" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E145" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F145">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C146" s="13" t="s">
-        <v>100</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C146" s="13"/>
       <c r="D146" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E146" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B147" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C147" s="13" t="s">
-        <v>84</v>
-      </c>
+      <c r="C147" s="13"/>
       <c r="D147" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F147">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="13" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C148" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C148" s="13"/>
       <c r="D148" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E148" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="13" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C149" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C149" s="13"/>
       <c r="D149" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E149" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F149">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="13" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B150" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C150" s="13" t="s">
-        <v>98</v>
-      </c>
+      <c r="C150" s="13"/>
       <c r="D150" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="13" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C151" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C151" s="13"/>
       <c r="D151" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E151" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F151">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="13" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C152" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C152" s="13"/>
       <c r="D152" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F152">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="13" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C153" s="13" t="s">
-        <v>97</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C153" s="13"/>
       <c r="D153" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E153" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C154" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C154" s="13"/>
       <c r="D154" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F154">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="13" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C155" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C155" s="13"/>
       <c r="D155" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E155" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="13" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C156" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C156" s="13"/>
       <c r="D156" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="13" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C157" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C157" s="13"/>
       <c r="D157" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F157">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="13" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B158" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C158" s="13" t="s">
-        <v>84</v>
-      </c>
+      <c r="C158" s="13"/>
       <c r="D158" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E158" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="13" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C159" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C159" s="13"/>
       <c r="D159" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E159" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F159">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="13" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C160" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C160" s="13"/>
       <c r="D160" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E160" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F160">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="13" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C161" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C161" s="13"/>
       <c r="D161" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E161" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="13" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C162" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C162" s="13"/>
       <c r="D162" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E162" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F162">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="13" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C163" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C163" s="13"/>
       <c r="D163" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F163">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="13" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C164" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C164" s="13"/>
       <c r="D164" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="13" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C165" s="13" t="s">
-        <v>94</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C165" s="13"/>
       <c r="D165" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E165" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F165">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="13" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C166" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C166" s="13"/>
       <c r="D166" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E166" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F166">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="13" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C167" s="13" t="s">
-        <v>95</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C167" s="13"/>
       <c r="D167" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E167" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="13" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C168" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C168" s="13"/>
       <c r="D168" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F168">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="13" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C169" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C169" s="13"/>
       <c r="D169" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E169" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F169">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="13" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C170" s="13" t="s">
-        <v>94</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C170" s="13"/>
       <c r="D170" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E170" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="13" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C171" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C171" s="13"/>
       <c r="D171" s="14" t="s">
         <v>2</v>
       </c>
       <c r="E171" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F171">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="13" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C172" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C172" s="13"/>
       <c r="D172" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E172" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F172">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="13" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C173" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C173" s="13"/>
       <c r="D173" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E173" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F173">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="13" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C174" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C174" s="13"/>
       <c r="D174" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E174" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F174">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="13" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C175" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C175" s="13"/>
       <c r="D175" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F175">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="13" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C176" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C176" s="13"/>
       <c r="D176" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E176" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F176">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="13" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C177" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C177" s="13"/>
       <c r="D177" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F177">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="13" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C178" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C178" s="13"/>
       <c r="D178" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E178" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F178">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="13" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C179" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C179" s="13"/>
       <c r="D179" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E179" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="13" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C180" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C180" s="13"/>
       <c r="D180" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E180" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F180">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="13" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C181" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C181" s="13"/>
       <c r="D181" s="14" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E181" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F181">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="13" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C182" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C182" s="13"/>
       <c r="D182" s="14" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E182" s="14" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C183" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C183" s="13"/>
       <c r="D183" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183" s="14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F183">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="13" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C184" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C184" s="13"/>
       <c r="D184" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" s="14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F184">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="13" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C185" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C185" s="13"/>
       <c r="D185" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="F185">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C186" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C186" s="13"/>
       <c r="D186" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186" s="14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="F186">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="13" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C187" s="13" t="s">
-        <v>99</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C187" s="13"/>
       <c r="D187" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E187" s="14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="F187">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="13" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C188" s="13" t="s">
-        <v>100</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C188" s="13"/>
       <c r="D188" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" s="14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="F188">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="13" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C189" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C189" s="13"/>
       <c r="D189" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" s="14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="F189">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="13" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C190" s="13" t="s">
-        <v>98</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C190" s="13"/>
       <c r="D190" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" s="14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="F190">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="13" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C191" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C191" s="13"/>
       <c r="D191" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E191" s="14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="F191">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="13" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C192" s="13" t="s">
-        <v>97</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C192" s="13"/>
       <c r="D192" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E192" s="14" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="F192">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="13" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C193" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D193" s="14" t="s">
         <v>1</v>
       </c>
       <c r="E193" s="14" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="F193">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="13" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C194" s="13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D194" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E194" s="14" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="F194">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="13" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C195" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C195" s="13"/>
       <c r="D195" s="14" t="s">
         <v>1</v>
       </c>
       <c r="E195" s="14" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="F195">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="13" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C196" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C196" s="13"/>
       <c r="D196" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" s="14" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="F196">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="13" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C197" s="13" t="s">
-        <v>84</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C197" s="13"/>
       <c r="D197" s="14" t="s">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E197" s="14" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="F197">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="13" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C198" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C198" s="13"/>
+      <c r="D198" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E198" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="D198" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E198" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F198">
-        <v>0.5</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="13" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C199" s="13" t="s">
-        <v>96</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C199" s="13"/>
       <c r="D199" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E199" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F199">
-        <v>0.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="13" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C200" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C200" s="13"/>
+      <c r="D200" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E200" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="D200" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E200" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F200">
-        <v>0.5</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="13" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C201" s="13" t="s">
-        <v>94</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C201" s="13"/>
       <c r="D201" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E201" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F201">
-        <v>0.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="13" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C202" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C202" s="13"/>
+      <c r="D202" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E202" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="D202" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E202" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F202">
-        <v>0.5</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="13" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B203" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C203" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C203" s="13"/>
+      <c r="D203" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E203" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="D203" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E203" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F203">
-        <v>0.5</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="13" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B204" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C204" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C204" s="13"/>
+      <c r="D204" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E204" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="D204" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E204" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F204">
-        <v>0.5</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="13" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B205" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C205" s="13" t="s">
-        <v>95</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C205" s="13"/>
       <c r="D205" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F205">
-        <v>0.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="13" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C206" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" s="13"/>
+      <c r="D206" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E206" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="D206" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E206" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F206">
-        <v>0.5</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="13" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B207" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C207" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C207" s="13"/>
+      <c r="D207" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E207" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="D207" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E207" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F207">
-        <v>0.5</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="13" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B208" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C208" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C208" s="13"/>
+      <c r="D208" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E208" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D208" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E208" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F208">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
+    </row>
+    <row r="209" spans="1:5">
       <c r="A209" s="13" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B209" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C209" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C209" s="13"/>
+      <c r="D209" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E209" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D209" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E209" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F209">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
+    </row>
+    <row r="210" spans="1:5">
       <c r="A210" s="13" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C210" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C210" s="13"/>
+      <c r="D210" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E210" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D210" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E210" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F210">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
+    </row>
+    <row r="211" spans="1:5">
       <c r="A211" s="13" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B211" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C211" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C211" s="13"/>
+      <c r="D211" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E211" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D211" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E211" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F211">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
+    </row>
+    <row r="212" spans="1:5">
       <c r="A212" s="13" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C212" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C212" s="13"/>
+      <c r="D212" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E212" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D212" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E212" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F212">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
+    </row>
+    <row r="213" spans="1:5">
       <c r="A213" s="13" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B213" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C213" s="13" t="s">
-        <v>97</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C213" s="13"/>
       <c r="D213" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E213" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F213">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
       <c r="A214" s="13" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C214" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C214" s="13"/>
+      <c r="D214" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E214" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D214" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E214" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F214">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
+    </row>
+    <row r="215" spans="1:5">
       <c r="A215" s="13" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B215" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C215" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C215" s="13"/>
+      <c r="D215" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E215" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D215" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E215" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F215">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
+    </row>
+    <row r="216" spans="1:5">
       <c r="A216" s="13" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C216" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C216" s="13"/>
+      <c r="D216" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E216" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D216" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E216" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F216">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
+    </row>
+    <row r="217" spans="1:5">
       <c r="A217" s="13" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B217" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C217" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C217" s="13"/>
+      <c r="D217" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E217" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D217" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E217" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F217">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
+    </row>
+    <row r="218" spans="1:5">
       <c r="A218" s="13" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C218" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C218" s="13"/>
+      <c r="D218" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E218" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D218" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E218" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F218">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
+    </row>
+    <row r="219" spans="1:5">
       <c r="A219" s="13" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B219" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C219" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" s="13"/>
+      <c r="D219" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E219" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D219" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E219" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F219">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
+    </row>
+    <row r="220" spans="1:5">
       <c r="A220" s="13" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C220" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C220" s="13"/>
+      <c r="D220" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E220" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D220" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E220" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F220">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
+    </row>
+    <row r="221" spans="1:5">
       <c r="A221" s="13" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B221" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C221" s="13" t="s">
-        <v>94</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C221" s="13"/>
       <c r="D221" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E221" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F221">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
       <c r="A222" s="13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B222" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C222" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C222" s="13"/>
+      <c r="D222" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E222" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D222" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E222" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F222">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
+    </row>
+    <row r="223" spans="1:5">
       <c r="A223" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B223" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C223" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C223" s="13"/>
+      <c r="D223" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E223" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D223" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E223" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F223">
-        <v>0.25</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E223">
-    <sortState ref="A3:E232">
-      <sortCondition descending="1" ref="E2:E232"/>
+  <autoFilter ref="A1:F1">
+    <sortState ref="A2:F223">
+      <sortCondition ref="E1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
